--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7567</v>
+        <v>7.7294</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2824</v>
+        <v>7.489</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4743</v>
+        <v>0.2404</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2205</v>
+        <v>3.1851</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.1238</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2121</v>
+        <v>3.3089</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0872</v>
+        <v>3.2204</v>
       </c>
       <c r="K2" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L2" t="n">
-        <v>2.9272</v>
+        <v>3.0562</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1334</v>
+        <v>-0.0353</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1515</v>
+        <v>-0.288</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2849</v>
+        <v>0.2527</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4839</v>
+        <v>-0.4699</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5959</v>
+        <v>0.6055</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0798</v>
+        <v>-1.0753</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2196</v>
+        <v>3.2616</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3798</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0872</v>
+        <v>3.0937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8310999999999999</v>
+        <v>1.0625</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2561</v>
+        <v>2.0313</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5983</v>
+        <v>2.5743</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5603</v>
+        <v>1.5451</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0379</v>
+        <v>1.0292</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6653</v>
+        <v>0.7675</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2614</v>
+        <v>1.3266</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5961</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9329</v>
+        <v>1.8068</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2989</v>
+        <v>0.2185</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6341</v>
+        <v>1.5883</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9096</v>
+        <v>0.881</v>
       </c>
       <c r="T3" t="n">
-        <v>0.467</v>
+        <v>0.4818</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4426</v>
+        <v>0.3992</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6207</v>
+        <v>-0.5563</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7869</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3197</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4662</v>
+        <v>0.349</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21</v>
+        <v>0.3282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2562</v>
+        <v>0.0207</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0343</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1094</v>
+        <v>0.0682</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9248</v>
+        <v>0.9011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8434</v>
+        <v>0.9257</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6034</v>
+        <v>0.6826</v>
       </c>
       <c r="L4" t="n">
-        <v>0.24</v>
+        <v>0.2432</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1909</v>
+        <v>0.0436</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.494</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3686</v>
+        <v>-0.3677</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0468</v>
+        <v>0.0646</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4154</v>
+        <v>-0.4323</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.9999</v>
+        <v>-2.0053</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3197</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="5">
@@ -799,28 +799,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4498</v>
+        <v>-0.4884</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.977</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1852</v>
+        <v>-1.4654</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7181</v>
+        <v>0.6966</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5042</v>
+        <v>-0.5239</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2223</v>
+        <v>1.2206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6491</v>
+        <v>0.8043</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1527</v>
+        <v>-0.0306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8018</v>
+        <v>0.835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.1077</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3515</v>
+        <v>-0.4933</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>0.672</v>
+        <v>0.6644</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8874</v>
+        <v>1.8726</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2154</v>
+        <v>-1.2082</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6811</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8393</v>
+        <v>-1.9021</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7141</v>
+        <v>-0.6669</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.166</v>
+        <v>-2.8308</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4519</v>
+        <v>2.1639</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9218</v>
+        <v>0.9534</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5959</v>
+        <v>-1.5753</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5177</v>
+        <v>2.5287</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8249</v>
+        <v>-0.6297</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1086</v>
+        <v>-1.9755</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2836</v>
+        <v>1.3457</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7467</v>
+        <v>1.5831</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2341</v>
+        <v>1.183</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1955</v>
+        <v>-0.2129</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.54</v>
+        <v>-0.5011</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3445</v>
+        <v>0.2882</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5602</v>
+        <v>0.54</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9724</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.407</v>
+        <v>-3.1708</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4457</v>
+        <v>2.1984</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2808</v>
+        <v>0.2187</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4927</v>
+        <v>-1.5513</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7735</v>
+        <v>1.77</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3304</v>
+        <v>-1.2262</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3342</v>
+        <v>-1.2751</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6112</v>
+        <v>1.4449</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1585</v>
+        <v>-0.2762</v>
       </c>
       <c r="O8" t="n">
-        <v>1.7697</v>
+        <v>1.7212</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5816</v>
+        <v>-0.5748</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2755</v>
+        <v>-0.2446</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3061</v>
+        <v>-0.3302</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7822</v>
+        <v>-1.7914</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5321</v>
+        <v>-2.4292</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7499</v>
+        <v>0.6378</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6829</v>
+        <v>1.6367</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6242</v>
+        <v>-0.6471</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3071</v>
+        <v>2.2838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0419</v>
+        <v>0.0655</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M9" t="n">
-        <v>1.641</v>
+        <v>1.5712</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6272</v>
+        <v>1.5948</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6649</v>
+        <v>-0.6491</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5734</v>
+        <v>-0.5473</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0914</v>
+        <v>-0.1018</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9387</v>
+        <v>-1.9694</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4949</v>
+        <v>-2.3569</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5562</v>
+        <v>0.3874</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7913</v>
+        <v>0.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2817</v>
+        <v>-0.3208</v>
       </c>
       <c r="I10" t="n">
-        <v>1.073</v>
+        <v>1.1008</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7923</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1543</v>
+        <v>-0.0888</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5835</v>
+        <v>1.4922</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3563</v>
+        <v>0.3027</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2273</v>
+        <v>1.1896</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3302</v>
+        <v>-0.3336</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7023</v>
+        <v>-0.671</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3722</v>
+        <v>0.3373</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7182</v>
+        <v>-6.6889</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5247</v>
+        <v>-5.327</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1935</v>
+        <v>-1.362</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.445</v>
+        <v>-2.4204</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4088</v>
+        <v>-2.4287</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0362</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4083</v>
+        <v>-2.3007</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6941</v>
+        <v>-1.6446</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6561</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0367</v>
+        <v>-0.1197</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7147</v>
+        <v>-0.7842</v>
       </c>
       <c r="O11" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4132</v>
+        <v>-0.4049</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1155</v>
+        <v>-0.1052</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2977</v>
+        <v>-0.2997</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9541999999999993</v>
+        <v>-1.0974</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7659</v>
+        <v>-5.950099999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8116</v>
+        <v>4.8525</v>
       </c>
       <c r="G12" t="n">
-        <v>9.102899999999998</v>
+        <v>8.901599999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.929500000000001</v>
+        <v>-5.249699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>14.0322</v>
+        <v>14.1515</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2309000000000005</v>
+        <v>1.222500000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.240899999999999</v>
+        <v>-3.6915</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4717</v>
+        <v>4.913999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>8.8719</v>
+        <v>7.6791</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6886000000000001</v>
+        <v>-1.5584</v>
       </c>
       <c r="O12" t="n">
-        <v>9.560700000000001</v>
+        <v>9.2376</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.0015</v>
+        <v>-4.8685</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.0048</v>
+        <v>-15.5788</v>
       </c>
       <c r="R12" t="n">
-        <v>11.003</v>
+        <v>10.7105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4563</v>
+        <v>-1.4675</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7903999999999998</v>
+        <v>0.9553</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2465</v>
+        <v>-2.4228</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.5993</v>
+        <v>-3.6633</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2176</v>
+        <v>7.4513</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.8168</v>
+        <v>-11.1145</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7294</v>
+        <v>8.0131</v>
       </c>
       <c r="E2" t="n">
-        <v>7.489</v>
+        <v>7.3893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2404</v>
+        <v>0.6237</v>
       </c>
       <c r="G2" t="n">
         <v>3.1851</v>
@@ -610,13 +610,13 @@
         <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4699</v>
+        <v>-0.1862</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6055</v>
+        <v>0.5058</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0753</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>3.2616</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0937</v>
+        <v>2.7166</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0625</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0313</v>
+        <v>2.0528</v>
       </c>
       <c r="G3" t="n">
         <v>2.5743</v>
@@ -688,13 +688,13 @@
         <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.881</v>
+        <v>0.5039</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4818</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3992</v>
+        <v>0.4208</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5563</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.349</v>
+        <v>0.6696</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3282</v>
+        <v>0.6273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0207</v>
+        <v>0.0423</v>
       </c>
       <c r="G4" t="n">
         <v>0.9693000000000001</v>
@@ -766,13 +766,13 @@
         <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3677</v>
+        <v>-0.0471</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0646</v>
+        <v>0.3636</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4323</v>
+        <v>-0.4107</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0053</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4884</v>
+        <v>-0.6083</v>
       </c>
       <c r="E6" t="n">
-        <v>0.977</v>
+        <v>-2.4321</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4654</v>
+        <v>1.8238</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6966</v>
+        <v>0.9534</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5239</v>
+        <v>-1.5753</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2206</v>
+        <v>2.5287</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8043</v>
+        <v>-0.6297</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0306</v>
+        <v>-1.9755</v>
       </c>
       <c r="L6" t="n">
-        <v>0.835</v>
+        <v>1.3457</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1077</v>
+        <v>1.5831</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4933</v>
+        <v>0.4001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3856</v>
+        <v>1.183</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1684</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.921</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7526</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6644</v>
+        <v>-0.1544</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8726</v>
+        <v>-0.1024</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2082</v>
+        <v>-0.0519</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6811</v>
+        <v>0.54</v>
       </c>
       <c r="W6" t="n">
         <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9021</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6669</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8308</v>
+        <v>-3.1708</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1639</v>
+        <v>2.3869</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9534</v>
+        <v>0.2187</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5753</v>
+        <v>-1.5513</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5287</v>
+        <v>1.77</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6297</v>
+        <v>-1.2262</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9755</v>
+        <v>-1.2751</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3457</v>
+        <v>0.0489</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5831</v>
+        <v>1.4449</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4001</v>
+        <v>-0.2762</v>
       </c>
       <c r="O7" t="n">
-        <v>1.183</v>
+        <v>1.7212</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9474</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.921</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2129</v>
+        <v>-0.3862</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5011</v>
+        <v>-0.2446</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2882</v>
+        <v>-0.1417</v>
       </c>
       <c r="V7" t="n">
-        <v>0.54</v>
+        <v>0.9416</v>
       </c>
       <c r="W7" t="n">
         <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6811</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9724</v>
+        <v>-1.0686</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1708</v>
+        <v>-0.1195</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1984</v>
+        <v>-0.9492</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2187</v>
+        <v>0.6966</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5513</v>
+        <v>-0.5239</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>1.2206</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2262</v>
+        <v>0.8043</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2751</v>
+        <v>-0.0306</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0489</v>
+        <v>0.835</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4449</v>
+        <v>-0.1077</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2762</v>
+        <v>-0.4933</v>
       </c>
       <c r="O8" t="n">
-        <v>1.7212</v>
+        <v>0.3856</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5579</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5748</v>
+        <v>0.0842</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2446</v>
+        <v>0.7762</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3302</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9416</v>
+        <v>-0.6811</v>
       </c>
       <c r="W8" t="n">
         <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2795</v>
+        <v>-1.9021</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7914</v>
+        <v>-1.2643</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4292</v>
+        <v>-2.2298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6378</v>
+        <v>0.9655</v>
       </c>
       <c r="G9" t="n">
         <v>1.6367</v>
@@ -1156,13 +1156,13 @@
         <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6491</v>
+        <v>-0.1221</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5473</v>
+        <v>-0.3479</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1018</v>
+        <v>0.2259</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2211</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9694</v>
+        <v>-1.6766</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3569</v>
+        <v>-2.0578</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3874</v>
+        <v>0.3812</v>
       </c>
       <c r="G10" t="n">
         <v>0.78</v>
@@ -1234,13 +1234,13 @@
         <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3336</v>
+        <v>-0.0408</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.671</v>
+        <v>-0.3719</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3373</v>
+        <v>0.3311</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8316</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6889</v>
+        <v>-6.0739</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.327</v>
+        <v>-4.9283</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.362</v>
+        <v>-1.1456</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4204</v>
@@ -1312,13 +1312,13 @@
         <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4049</v>
+        <v>0.2102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1052</v>
+        <v>0.2935</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2997</v>
+        <v>-0.0833</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1111</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0974</v>
+        <v>0.2317</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.950099999999997</v>
+        <v>-5.949999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.8525</v>
+        <v>6.1814</v>
       </c>
       <c r="G12" t="n">
         <v>8.901599999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.249699999999999</v>
+        <v>-5.2497</v>
       </c>
       <c r="I12" t="n">
         <v>14.1515</v>
       </c>
       <c r="J12" t="n">
-        <v>1.222500000000001</v>
+        <v>1.2225</v>
       </c>
       <c r="K12" t="n">
         <v>-3.6915</v>
@@ -1390,13 +1390,13 @@
         <v>10.7105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4675</v>
+        <v>-0.1385000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9553</v>
+        <v>0.9553999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4228</v>
+        <v>-1.0938</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6633</v>
